--- a/dk18.xlsx
+++ b/dk18.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CE140D-9D30-4CF1-ABAE-55D45D5BF3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2BF715-5AEB-4BF3-B6DD-577086AB6F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-18120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dk18" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3209" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3220" uniqueCount="235">
   <si>
     <t>가산DK 18층 라운지</t>
   </si>
@@ -158,6 +158,9 @@
     <t>주해란</t>
   </si>
   <si>
+    <t>김선호</t>
+  </si>
+  <si>
     <t>전수민</t>
   </si>
   <si>
@@ -309,6 +312,9 @@
     <t>최슬기</t>
   </si>
   <si>
+    <t>허혜정</t>
+  </si>
+  <si>
     <t>오슬기A</t>
   </si>
   <si>
@@ -368,6 +374,9 @@
     <t>김덕원</t>
   </si>
   <si>
+    <t>정인모</t>
+  </si>
+  <si>
     <t>최승헌</t>
   </si>
   <si>
@@ -510,6 +519,9 @@
     <t>이혜진</t>
   </si>
   <si>
+    <t>최다빈</t>
+  </si>
+  <si>
     <t>전가연</t>
   </si>
   <si>
@@ -732,22 +744,6 @@
   </si>
   <si>
     <t>박성범</t>
-  </si>
-  <si>
-    <t>정인모</t>
-    <phoneticPr fontId="96" type="noConversion"/>
-  </si>
-  <si>
-    <t>최다빈</t>
-    <phoneticPr fontId="96" type="noConversion"/>
-  </si>
-  <si>
-    <t>허혜정</t>
-    <phoneticPr fontId="96" type="noConversion"/>
-  </si>
-  <si>
-    <t>김선호</t>
-    <phoneticPr fontId="96" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2896,7 +2892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3190,9 +3186,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="93" fillId="71" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3945,13 +3938,21 @@
       <c r="AJ4" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AM4" s="43"/>
-      <c r="AN4" s="44"/>
+      <c r="AM4" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="44" t="s">
+        <v>1</v>
+      </c>
       <c r="AO4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="AQ4" s="43"/>
-      <c r="AR4" s="44"/>
+      <c r="AQ4" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="44" t="s">
+        <v>1</v>
+      </c>
       <c r="AU4" s="43" t="s">
         <v>7</v>
       </c>
@@ -4089,10 +4090,18 @@
       <c r="AJ5" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="AM5" s="45"/>
-      <c r="AN5" s="46"/>
-      <c r="AQ5" s="45"/>
-      <c r="AR5" s="46"/>
+      <c r="AM5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="46" t="s">
+        <v>1</v>
+      </c>
       <c r="AU5" s="45" t="s">
         <v>1</v>
       </c>
@@ -4764,46 +4773,50 @@
       <c r="AU9" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="AV9" s="40"/>
+      <c r="AV9" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="AX9" s="6" t="s">
         <v>1</v>
       </c>
       <c r="AY9" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="AZ9" s="40"/>
-      <c r="BC9" s="99" t="s">
-        <v>234</v>
+      <c r="AZ9" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC9" s="40" t="s">
+        <v>43</v>
       </c>
       <c r="BD9" s="40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="BG9" s="40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BH9" s="40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="BI9" s="5" t="s">
         <v>1</v>
       </c>
       <c r="BK9" s="40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="BL9" s="40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BO9" s="40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="BP9" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="BS9" s="40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="BT9" s="40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="BW9" s="34" t="s">
         <v>1</v>
@@ -4930,14 +4943,18 @@
       <c r="AU10" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="AV10" s="41"/>
+      <c r="AV10" s="41" t="s">
+        <v>1</v>
+      </c>
       <c r="AX10" s="6" t="s">
         <v>1</v>
       </c>
       <c r="AY10" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="AZ10" s="41"/>
+      <c r="AZ10" s="41" t="s">
+        <v>1</v>
+      </c>
       <c r="BC10" s="41" t="s">
         <v>1</v>
       </c>
@@ -5096,14 +5113,18 @@
       <c r="AU11" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="AV11" s="42"/>
+      <c r="AV11" s="42" t="s">
+        <v>1</v>
+      </c>
       <c r="AX11" s="6" t="s">
         <v>1</v>
       </c>
       <c r="AY11" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="AZ11" s="42"/>
+      <c r="AZ11" s="42" t="s">
+        <v>1</v>
+      </c>
       <c r="BC11" s="42" t="s">
         <v>1</v>
       </c>
@@ -5239,49 +5260,49 @@
         <v>1</v>
       </c>
       <c r="AI12" s="47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AJ12" s="47" t="s">
         <v>1</v>
       </c>
       <c r="AM12" s="47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AN12" s="47" t="s">
         <v>1</v>
       </c>
       <c r="AQ12" s="47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AR12" s="47" t="s">
         <v>1</v>
       </c>
       <c r="AU12" s="47" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AV12" s="47" t="s">
         <v>1</v>
       </c>
       <c r="AY12" s="47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AZ12" s="47" t="s">
         <v>1</v>
       </c>
       <c r="BC12" s="47" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BD12" s="47" t="s">
         <v>1</v>
       </c>
       <c r="BK12" s="47" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BL12" s="47" t="s">
         <v>1</v>
       </c>
       <c r="BO12" s="47" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="BP12" s="47" t="s">
         <v>1</v>
@@ -5370,19 +5391,19 @@
         <v>1</v>
       </c>
       <c r="W13" s="31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="X13" s="33" t="s">
         <v>1</v>
       </c>
       <c r="Y13" s="31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z13" s="33" t="s">
         <v>1</v>
       </c>
       <c r="AA13" s="31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB13" s="33" t="s">
         <v>1</v>
@@ -5489,13 +5510,13 @@
         <v>1</v>
       </c>
       <c r="AI14" s="48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AJ14" s="48" t="s">
         <v>1</v>
       </c>
       <c r="BO14" s="49" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="BP14" s="49" t="s">
         <v>1</v>
@@ -5513,7 +5534,7 @@
         <v>1</v>
       </c>
       <c r="BW14" s="31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="BX14" s="32" t="s">
         <v>1</v>
@@ -5620,34 +5641,34 @@
         <v>1</v>
       </c>
       <c r="AJ15" s="40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM15" s="40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AN15" s="40" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AQ15" s="40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AR15" s="40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AU15" s="40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AV15" s="40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AY15" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AZ15" s="5" t="s">
         <v>1</v>
       </c>
       <c r="BB15" s="31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BC15" s="32" t="s">
         <v>1</v>
@@ -5659,25 +5680,25 @@
         <v>1</v>
       </c>
       <c r="BH15" s="40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BK15" s="40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BL15" s="40" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BO15" s="40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BP15" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BS15" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BT15" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BW15" s="34" t="s">
         <v>1</v>
@@ -6121,64 +6142,64 @@
         <v>1</v>
       </c>
       <c r="AJ18" s="40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM18" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN18" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ18" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="AR18" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU18" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV18" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY18" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="AZ18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC18" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD18" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE18" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="BH18" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="BK18" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL18" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="BO18" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="AN18" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ18" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="AR18" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="AU18" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV18" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY18" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="AZ18" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BB18" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="BC18" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD18" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE18" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH18" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="BK18" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL18" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="BO18" s="40" t="s">
-        <v>79</v>
-      </c>
       <c r="BP18" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BS18" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BT18" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BW18" s="34" t="s">
         <v>1</v>
@@ -6538,55 +6559,55 @@
         <v>1</v>
       </c>
       <c r="AI21" s="40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AJ21" s="40" t="s">
         <v>1</v>
       </c>
       <c r="AM21" s="40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AN21" s="40" t="s">
         <v>1</v>
       </c>
       <c r="AQ21" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="AR21" s="99" t="s">
-        <v>233</v>
+        <v>92</v>
+      </c>
+      <c r="AR21" s="40" t="s">
+        <v>93</v>
       </c>
       <c r="AU21" s="40" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AV21" s="40" t="s">
         <v>1</v>
       </c>
       <c r="AY21" s="40" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AZ21" s="5" t="s">
         <v>1</v>
       </c>
       <c r="BH21" s="40" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="BK21" s="40" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="BL21" s="40" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BO21" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BP21" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BS21" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BT21" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BW21" s="34" t="s">
         <v>1</v>
@@ -6987,7 +7008,7 @@
         <v>1</v>
       </c>
       <c r="Z25" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AA25" s="50" t="s">
         <v>1</v>
@@ -7071,7 +7092,7 @@
         <v>1</v>
       </c>
       <c r="BB25" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BC25" s="50" t="s">
         <v>1</v>
@@ -8137,7 +8158,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="54" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L30" s="55" t="s">
         <v>1</v>
@@ -8158,116 +8179,116 @@
         <v>1</v>
       </c>
       <c r="R30" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="S30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="T30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="U30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="V30" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="W30" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE30" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG30" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH30" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI30" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ30" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="AK30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN30" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU30" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB30" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="S30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="T30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="U30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="V30" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="W30" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="X30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE30" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF30" s="60" t="s">
-        <v>100</v>
-      </c>
-      <c r="AG30" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH30" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI30" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ30" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN30" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AP30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AR30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AS30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AT30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AU30" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="AV30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AW30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AY30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AZ30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BB30" s="50" t="s">
-        <v>97</v>
-      </c>
       <c r="BC30" s="50" t="s">
         <v>1</v>
       </c>
@@ -8332,7 +8353,7 @@
         <v>1</v>
       </c>
       <c r="BX30" s="31" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BY30" s="32" t="s">
         <v>1</v>
@@ -8555,7 +8576,7 @@
         <v>1</v>
       </c>
       <c r="AP32" s="48" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AQ32" s="48" t="s">
         <v>1</v>
@@ -8573,31 +8594,31 @@
         <v>1</v>
       </c>
       <c r="BB32" s="49" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BC32" s="49" t="s">
         <v>1</v>
       </c>
       <c r="BG32" s="48" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BH32" s="48" t="s">
         <v>1</v>
       </c>
       <c r="BK32" s="48" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BL32" s="48" t="s">
         <v>1</v>
       </c>
       <c r="BO32" s="48" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BP32" s="48" t="s">
         <v>1</v>
       </c>
       <c r="BV32" s="31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BW32" s="32" t="s">
         <v>1</v>
@@ -8713,7 +8734,7 @@
         <v>1</v>
       </c>
       <c r="AO33" s="69" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AP33" s="69" t="s">
         <v>1</v>
@@ -8722,7 +8743,7 @@
         <v>1</v>
       </c>
       <c r="AR33" s="71" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AS33" s="69" t="s">
         <v>1</v>
@@ -8733,35 +8754,35 @@
       <c r="AU33" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="AY33" s="99" t="s">
-        <v>231</v>
+      <c r="AY33" s="40" t="s">
+        <v>113</v>
       </c>
       <c r="AZ33" s="40" t="s">
         <v>1</v>
       </c>
       <c r="BC33" s="40" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="BD33" s="40" t="s">
         <v>1</v>
       </c>
       <c r="BG33" s="40" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="BH33" s="40" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="BK33" s="40" t="s">
         <v>1</v>
       </c>
       <c r="BL33" s="40" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="BO33" s="40" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="BP33" s="40" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="BS33" s="40" t="s">
         <v>1</v>
@@ -8793,7 +8814,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="54" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L34" s="55" t="s">
         <v>1</v>
@@ -8883,7 +8904,7 @@
         <v>1</v>
       </c>
       <c r="AO34" s="71" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP34" s="69" t="s">
         <v>1</v>
@@ -8892,7 +8913,7 @@
         <v>1</v>
       </c>
       <c r="AR34" s="71" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AS34" s="69" t="s">
         <v>1</v>
@@ -9089,7 +9110,7 @@
         <v>1</v>
       </c>
       <c r="BV35" s="31" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="BW35" s="32" t="s">
         <v>1</v>
@@ -9211,34 +9232,34 @@
         <v>1</v>
       </c>
       <c r="AZ36" s="40" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="BC36" s="40" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="BD36" s="40" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="BG36" s="40" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="BH36" s="40" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="BK36" s="40" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="BL36" s="40" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="BO36" s="40" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="BP36" s="40" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="BS36" s="40" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="BV36" s="34" t="s">
         <v>1</v>
@@ -9458,7 +9479,7 @@
         <v>1</v>
       </c>
       <c r="R38" s="54" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="S38" s="55" t="s">
         <v>1</v>
@@ -9512,7 +9533,7 @@
         <v>1</v>
       </c>
       <c r="AJ38" s="54" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AK38" s="55" t="s">
         <v>1</v>
@@ -9721,34 +9742,34 @@
         <v>1</v>
       </c>
       <c r="AZ39" s="40" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="BC39" s="40" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="BD39" s="40" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BG39" s="40" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="BH39" s="40" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="BK39" s="40" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="BL39" s="40" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="BO39" s="40" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="BP39" s="40" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="BS39" s="40" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="BV39" s="34" t="s">
         <v>1</v>
@@ -9947,7 +9968,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="54" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L41" s="55" t="s">
         <v>1</v>
@@ -10234,25 +10255,25 @@
         <v>1</v>
       </c>
       <c r="BC42" s="43" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="BD42" s="44" t="s">
         <v>1</v>
       </c>
       <c r="BG42" s="43" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="BH42" s="44" t="s">
         <v>1</v>
       </c>
       <c r="BK42" s="43" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="BL42" s="44" t="s">
         <v>1</v>
       </c>
       <c r="BO42" s="43" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="BP42" s="44" t="s">
         <v>1</v>
@@ -11382,13 +11403,13 @@
         <v>1</v>
       </c>
       <c r="X49" s="81" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Y49" s="82" t="s">
         <v>1</v>
       </c>
       <c r="Z49" s="85" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AA49" s="50" t="s">
         <v>1</v>
@@ -11403,13 +11424,13 @@
         <v>1</v>
       </c>
       <c r="AE49" s="34" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AF49" s="87" t="s">
         <v>1</v>
       </c>
       <c r="AG49" s="34" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AH49" s="87" t="s">
         <v>1</v>
@@ -11429,10 +11450,10 @@
         <v>1</v>
       </c>
       <c r="C50" s="40" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F50" s="89" t="s">
         <v>1</v>
@@ -11462,16 +11483,14 @@
         <v>1</v>
       </c>
       <c r="R50" s="40" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="S50" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="U50" s="40" t="s">
-        <v>155</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="U50" s="40"/>
       <c r="V50" s="40" t="s">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="X50" s="81" t="s">
         <v>1</v>
@@ -11492,16 +11511,16 @@
         <v>1</v>
       </c>
       <c r="AI50" s="44" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AK50" s="6" t="s">
         <v>1</v>
       </c>
       <c r="AL50" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="AM50" s="99" t="s">
-        <v>232</v>
+        <v>160</v>
+      </c>
+      <c r="AM50" s="40" t="s">
+        <v>161</v>
       </c>
       <c r="AX50" s="3" t="s">
         <v>1</v>
@@ -11550,9 +11569,7 @@
       <c r="S51" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="U51" s="41" t="s">
-        <v>1</v>
-      </c>
+      <c r="U51" s="41"/>
       <c r="V51" s="41" t="s">
         <v>1</v>
       </c>
@@ -11587,13 +11604,13 @@
         <v>1</v>
       </c>
       <c r="AP51" s="43" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="AQ51" s="44" t="s">
         <v>1</v>
       </c>
       <c r="AT51" s="43" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AU51" s="44" t="s">
         <v>1</v>
@@ -11645,9 +11662,7 @@
       <c r="S52" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="U52" s="42" t="s">
-        <v>1</v>
-      </c>
+      <c r="U52" s="42"/>
       <c r="V52" s="42" t="s">
         <v>1</v>
       </c>
@@ -11702,19 +11717,19 @@
         <v>1</v>
       </c>
       <c r="C53" s="40" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F53" s="89" t="s">
         <v>1</v>
       </c>
       <c r="G53" s="40" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I53" s="40" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J53" s="89" t="s">
         <v>1</v>
@@ -11735,16 +11750,16 @@
         <v>1</v>
       </c>
       <c r="R53" s="40" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="S53" s="40" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U53" s="40" t="s">
         <v>1</v>
       </c>
       <c r="V53" s="40" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="X53" s="81" t="s">
         <v>1</v>
@@ -11765,25 +11780,25 @@
         <v>1</v>
       </c>
       <c r="AI53" s="44" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AL53" s="40" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AM53" s="40" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AP53" s="40" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="AQ53" s="40" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AT53" s="40" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="AU53" s="40" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AX53" s="3" t="s">
         <v>1</v>
@@ -11978,19 +11993,19 @@
         <v>1</v>
       </c>
       <c r="C56" s="40" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D56" s="40" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F56" s="89" t="s">
         <v>1</v>
       </c>
       <c r="G56" s="40" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I56" s="40" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J56" s="89" t="s">
         <v>1</v>
@@ -12008,10 +12023,10 @@
         <v>1</v>
       </c>
       <c r="R56" s="40" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="S56" s="40" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="T56" s="6" t="s">
         <v>1</v>
@@ -12020,7 +12035,7 @@
         <v>1</v>
       </c>
       <c r="V56" s="40" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="X56" s="81" t="s">
         <v>1</v>
@@ -12041,28 +12056,28 @@
         <v>1</v>
       </c>
       <c r="AI56" s="44" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AL56" s="40" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AM56" s="40" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AP56" s="40" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AQ56" s="40" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AS56" s="6" t="s">
         <v>1</v>
       </c>
       <c r="AT56" s="40" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AU56" s="40" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AX56" s="3" t="s">
         <v>1</v>
@@ -12263,13 +12278,13 @@
         <v>1</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D59" s="47" t="s">
         <v>1</v>
       </c>
       <c r="G59" s="49" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H59" s="49" t="s">
         <v>1</v>
@@ -12278,13 +12293,13 @@
         <v>1</v>
       </c>
       <c r="U59" s="47" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="V59" s="47" t="s">
         <v>1</v>
       </c>
       <c r="AK59" s="49" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AL59" s="49" t="s">
         <v>1</v>
@@ -12293,7 +12308,7 @@
         <v>1</v>
       </c>
       <c r="AT59" s="47" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AU59" s="47" t="s">
         <v>1</v>
@@ -12315,28 +12330,28 @@
         <v>1</v>
       </c>
       <c r="C61" s="48" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D61" s="48" t="s">
         <v>1</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O61" s="48" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="P61" s="48" t="s">
         <v>1</v>
       </c>
       <c r="R61" s="48" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="S61" s="48" t="s">
         <v>1</v>
       </c>
       <c r="AM61" s="49" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AN61" s="49" t="s">
         <v>1</v>
@@ -12345,7 +12360,7 @@
         <v>1</v>
       </c>
       <c r="AT61" s="49" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AU61" s="49" t="s">
         <v>1</v>
@@ -12362,13 +12377,13 @@
         <v>1</v>
       </c>
       <c r="C62" s="40" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F62" s="40" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G62" s="89" t="s">
         <v>1</v>
@@ -12380,7 +12395,7 @@
         <v>1</v>
       </c>
       <c r="O62" s="40" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="P62" s="40" t="s">
         <v>1</v>
@@ -12389,10 +12404,10 @@
         <v>1</v>
       </c>
       <c r="R62" s="40" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="S62" s="40" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="T62" s="6" t="s">
         <v>1</v>
@@ -12404,13 +12419,13 @@
         <v>1</v>
       </c>
       <c r="X62" s="31" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Y62" s="88" t="s">
         <v>1</v>
       </c>
       <c r="Z62" s="31" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AA62" s="88" t="s">
         <v>1</v>
@@ -12431,34 +12446,34 @@
         <v>1</v>
       </c>
       <c r="AG62" s="31" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AH62" s="88" t="s">
         <v>1</v>
       </c>
       <c r="AI62" s="44" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AK62" s="6" t="s">
         <v>1</v>
       </c>
       <c r="AL62" s="40" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AM62" s="40" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AP62" s="40" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AQ62" s="40" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AT62" s="40" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AU62" s="40" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AX62" s="3" t="s">
         <v>1</v>
@@ -12683,19 +12698,19 @@
         <v>1</v>
       </c>
       <c r="C65" s="40" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F65" s="40" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G65" s="89" t="s">
         <v>1</v>
       </c>
       <c r="J65" s="93" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L65" s="89" t="s">
         <v>1</v>
@@ -12704,16 +12719,16 @@
         <v>1</v>
       </c>
       <c r="O65" s="40" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P65" s="40" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="R65" s="40" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S65" s="40" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="U65" s="89" t="s">
         <v>1</v>
@@ -12758,22 +12773,22 @@
         <v>1</v>
       </c>
       <c r="AL65" s="40" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AM65" s="40" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AP65" s="40" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AQ65" s="40" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AT65" s="40" t="s">
         <v>1</v>
       </c>
       <c r="AU65" s="40" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AX65" s="3" t="s">
         <v>1</v>
@@ -12986,13 +13001,13 @@
         <v>1</v>
       </c>
       <c r="C68" s="43" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D68" s="44" t="s">
         <v>1</v>
       </c>
       <c r="F68" s="43" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G68" s="44" t="s">
         <v>1</v>
@@ -13007,13 +13022,13 @@
         <v>1</v>
       </c>
       <c r="O68" s="43" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="P68" s="44" t="s">
         <v>1</v>
       </c>
       <c r="R68" s="43" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="S68" s="44" t="s">
         <v>1</v>
@@ -13058,13 +13073,13 @@
         <v>1</v>
       </c>
       <c r="AP68" s="43" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AQ68" s="44" t="s">
         <v>1</v>
       </c>
       <c r="AT68" s="43" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AU68" s="44" t="s">
         <v>1</v>
@@ -13640,7 +13655,7 @@
   <phoneticPr fontId="96" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CV3 A34:CV49 A33:AX33 AZ33:CV33 A12:CV20 A9:AU11 AW9:AY11 BA10:CV11 A51:CV52 A50:AL50 AN50:CV50 A56:CV75 A53:AL55 AN53:CV55 A22:CV32 A21:AQ21 AS21:CV21 A6:CV8 A4:AL5 AS4:CV5 AO4:AP5 BA9:BB9 BD9:CV9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CV49 A53:CV75 A50:T52 W50:CV52" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dk18.xlsx
+++ b/dk18.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2BF715-5AEB-4BF3-B6DD-577086AB6F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691D37D2-7DE9-4911-872D-9E8A47740048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7350" yWindow="-13995" windowWidth="17280" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dk18" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3220" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3204" uniqueCount="230">
   <si>
     <t>가산DK 18층 라운지</t>
   </si>
@@ -264,9 +264,6 @@
     <t>김민경</t>
   </si>
   <si>
-    <t>나하율</t>
-  </si>
-  <si>
     <t>주민수</t>
   </si>
   <si>
@@ -525,9 +522,6 @@
     <t>전가연</t>
   </si>
   <si>
-    <t>김경식</t>
-  </si>
-  <si>
     <t>정아름</t>
   </si>
   <si>
@@ -550,16 +544,10 @@
     <t>백혜미</t>
   </si>
   <si>
-    <t>정윤하</t>
-  </si>
-  <si>
     <t>남궁윤</t>
   </si>
   <si>
     <t>이주</t>
-  </si>
-  <si>
-    <t>김맑음이</t>
   </si>
   <si>
     <t>박난희</t>
@@ -637,9 +625,6 @@
   </si>
   <si>
     <t>광고네트워크전략팀</t>
-  </si>
-  <si>
-    <t>권민희</t>
   </si>
   <si>
     <t>박준영</t>
@@ -5682,23 +5667,21 @@
       <c r="BH15" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="BK15" s="40" t="s">
+      <c r="BK15" s="40"/>
+      <c r="BL15" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="BL15" s="40" t="s">
+      <c r="BO15" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="BO15" s="40" t="s">
+      <c r="BP15" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="BP15" s="40" t="s">
-        <v>80</v>
-      </c>
       <c r="BS15" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BT15" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BW15" s="34" t="s">
         <v>1</v>
@@ -5849,9 +5832,7 @@
       <c r="BH16" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="BK16" s="41" t="s">
-        <v>1</v>
-      </c>
+      <c r="BK16" s="41"/>
       <c r="BL16" s="41" t="s">
         <v>1</v>
       </c>
@@ -6016,9 +5997,7 @@
       <c r="BH17" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="BK17" s="42" t="s">
-        <v>1</v>
-      </c>
+      <c r="BK17" s="42"/>
       <c r="BL17" s="42" t="s">
         <v>1</v>
       </c>
@@ -6145,61 +6124,61 @@
         <v>67</v>
       </c>
       <c r="AM18" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN18" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ18" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="AN18" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ18" s="40" t="s">
+      <c r="AR18" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="AR18" s="40" t="s">
+      <c r="AU18" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="AU18" s="40" t="s">
+      <c r="AV18" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="AV18" s="40" t="s">
+      <c r="AY18" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="AY18" s="40" t="s">
+      <c r="AZ18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC18" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD18" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE18" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="BH18" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="AZ18" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BB18" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="BC18" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD18" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE18" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH18" s="40" t="s">
+      <c r="BK18" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="BK18" s="40" t="s">
+      <c r="BL18" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="BL18" s="40" t="s">
-        <v>89</v>
-      </c>
       <c r="BO18" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BP18" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BS18" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BT18" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BW18" s="34" t="s">
         <v>1</v>
@@ -6559,55 +6538,55 @@
         <v>1</v>
       </c>
       <c r="AI21" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ21" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM21" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="AJ21" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM21" s="40" t="s">
+      <c r="AN21" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ21" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="AN21" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ21" s="40" t="s">
+      <c r="AR21" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="AR21" s="40" t="s">
+      <c r="AU21" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AU21" s="40" t="s">
+      <c r="AV21" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY21" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="AV21" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AY21" s="40" t="s">
+      <c r="AZ21" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BH21" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="AZ21" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH21" s="40" t="s">
+      <c r="BK21" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BK21" s="40" t="s">
+      <c r="BL21" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="BL21" s="40" t="s">
-        <v>98</v>
-      </c>
       <c r="BO21" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BP21" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BS21" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BT21" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BW21" s="34" t="s">
         <v>1</v>
@@ -7008,7 +6987,7 @@
         <v>1</v>
       </c>
       <c r="Z25" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AA25" s="50" t="s">
         <v>1</v>
@@ -7092,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="BB25" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BC25" s="50" t="s">
         <v>1</v>
@@ -8158,202 +8137,202 @@
         <v>1</v>
       </c>
       <c r="K30" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="L30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="M30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="N30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="O30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="P30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="R30" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="L30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="M30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="N30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="O30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="P30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="R30" s="54" t="s">
+      <c r="S30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="T30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="U30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="V30" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="W30" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD30" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE30" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="60" t="s">
         <v>101</v>
       </c>
-      <c r="S30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="T30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="U30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="V30" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="W30" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="X30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD30" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE30" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF30" s="60" t="s">
+      <c r="AG30" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH30" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI30" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ30" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="AG30" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH30" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI30" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ30" s="54" t="s">
+      <c r="AK30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN30" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU30" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB30" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC30" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD30" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE30" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF30" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BH30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BI30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX30" s="31" t="s">
         <v>103</v>
-      </c>
-      <c r="AK30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM30" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN30" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AP30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AR30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AS30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AT30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AU30" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="AV30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AW30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AY30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AZ30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BB30" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="BC30" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD30" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE30" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF30" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BI30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BJ30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BK30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BM30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BN30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BO30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BP30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BQ30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BR30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BS30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BT30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BU30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BV30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BW30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BX30" s="31" t="s">
-        <v>104</v>
       </c>
       <c r="BY30" s="32" t="s">
         <v>1</v>
@@ -8576,49 +8555,49 @@
         <v>1</v>
       </c>
       <c r="AP32" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="AQ32" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR32" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS32" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT32" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU32" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB32" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="AQ32" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="AR32" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="AS32" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="AT32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="AU32" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="BB32" s="49" t="s">
+      <c r="BC32" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG32" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="BC32" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG32" s="48" t="s">
+      <c r="BH32" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK32" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="BH32" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="BK32" s="48" t="s">
+      <c r="BL32" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO32" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="BL32" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="BO32" s="48" t="s">
+      <c r="BP32" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV32" s="31" t="s">
         <v>109</v>
-      </c>
-      <c r="BP32" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="BV32" s="31" t="s">
-        <v>110</v>
       </c>
       <c r="BW32" s="32" t="s">
         <v>1</v>
@@ -8734,55 +8713,55 @@
         <v>1</v>
       </c>
       <c r="AO33" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP33" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ33" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR33" s="71" t="s">
         <v>111</v>
       </c>
-      <c r="AP33" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ33" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AR33" s="71" t="s">
+      <c r="AS33" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT33" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU33" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY33" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="AS33" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="AT33" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AU33" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="AY33" s="40" t="s">
+      <c r="AZ33" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC33" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="AZ33" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="BC33" s="40" t="s">
+      <c r="BD33" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG33" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="BD33" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG33" s="40" t="s">
+      <c r="BH33" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="BH33" s="40" t="s">
+      <c r="BK33" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL33" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="BK33" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL33" s="40" t="s">
+      <c r="BO33" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="BO33" s="40" t="s">
+      <c r="BP33" s="40" t="s">
         <v>118</v>
-      </c>
-      <c r="BP33" s="40" t="s">
-        <v>119</v>
       </c>
       <c r="BS33" s="40" t="s">
         <v>1</v>
@@ -8814,106 +8793,106 @@
         <v>1</v>
       </c>
       <c r="K34" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="L34" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="M34" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="N34" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="O34" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="P34" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="R34" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="S34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="T34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="U34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V34" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="W34" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH34" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI34" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ34" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM34" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN34" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO34" s="71" t="s">
         <v>120</v>
       </c>
-      <c r="L34" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="M34" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="N34" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="O34" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="P34" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="R34" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="S34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="T34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="U34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V34" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="W34" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="X34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE34" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="63" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG34" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH34" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI34" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ34" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM34" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN34" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO34" s="71" t="s">
+      <c r="AP34" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ34" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR34" s="71" t="s">
         <v>121</v>
-      </c>
-      <c r="AP34" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ34" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AR34" s="71" t="s">
-        <v>122</v>
       </c>
       <c r="AS34" s="69" t="s">
         <v>1</v>
@@ -9110,7 +9089,7 @@
         <v>1</v>
       </c>
       <c r="BV35" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BW35" s="32" t="s">
         <v>1</v>
@@ -9232,34 +9211,34 @@
         <v>1</v>
       </c>
       <c r="AZ36" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="BC36" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="BC36" s="40" t="s">
+      <c r="BD36" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="BD36" s="40" t="s">
+      <c r="BG36" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="BG36" s="40" t="s">
+      <c r="BH36" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="BH36" s="40" t="s">
+      <c r="BK36" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="BK36" s="40" t="s">
+      <c r="BL36" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="BL36" s="40" t="s">
+      <c r="BO36" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="BO36" s="40" t="s">
+      <c r="BP36" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="BP36" s="40" t="s">
+      <c r="BS36" s="40" t="s">
         <v>132</v>
-      </c>
-      <c r="BS36" s="40" t="s">
-        <v>133</v>
       </c>
       <c r="BV36" s="34" t="s">
         <v>1</v>
@@ -9479,61 +9458,61 @@
         <v>1</v>
       </c>
       <c r="R38" s="54" t="s">
+        <v>133</v>
+      </c>
+      <c r="S38" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="T38" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="U38" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="V38" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="W38" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X38" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y38" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD38" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE38" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG38" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH38" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI38" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ38" s="54" t="s">
         <v>134</v>
-      </c>
-      <c r="S38" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="T38" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="U38" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="V38" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="W38" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="X38" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y38" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA38" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB38" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC38" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD38" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE38" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF38" s="63" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH38" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI38" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ38" s="54" t="s">
-        <v>135</v>
       </c>
       <c r="AK38" s="55" t="s">
         <v>1</v>
@@ -9742,34 +9721,34 @@
         <v>1</v>
       </c>
       <c r="AZ39" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="BC39" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="BC39" s="40" t="s">
+      <c r="BD39" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="BD39" s="40" t="s">
+      <c r="BG39" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="BG39" s="40" t="s">
+      <c r="BH39" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="BH39" s="40" t="s">
+      <c r="BK39" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="BK39" s="40" t="s">
+      <c r="BL39" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="BL39" s="40" t="s">
+      <c r="BO39" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="BO39" s="40" t="s">
+      <c r="BP39" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="BP39" s="40" t="s">
+      <c r="BS39" s="40" t="s">
         <v>144</v>
-      </c>
-      <c r="BS39" s="40" t="s">
-        <v>145</v>
       </c>
       <c r="BV39" s="34" t="s">
         <v>1</v>
@@ -9968,7 +9947,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="54" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L41" s="55" t="s">
         <v>1</v>
@@ -10255,25 +10234,25 @@
         <v>1</v>
       </c>
       <c r="BC42" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="BD42" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG42" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="BD42" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG42" s="43" t="s">
+      <c r="BH42" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK42" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="BH42" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="BK42" s="43" t="s">
+      <c r="BL42" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO42" s="43" t="s">
         <v>149</v>
-      </c>
-      <c r="BL42" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="BO42" s="43" t="s">
-        <v>150</v>
       </c>
       <c r="BP42" s="44" t="s">
         <v>1</v>
@@ -11403,34 +11382,34 @@
         <v>1</v>
       </c>
       <c r="X49" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y49" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z49" s="85" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA49" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC49" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD49" s="86" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE49" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="Y49" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="85" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA49" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB49" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC49" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD49" s="86" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE49" s="34" t="s">
+      <c r="AF49" s="87" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG49" s="34" t="s">
         <v>152</v>
-      </c>
-      <c r="AF49" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG49" s="34" t="s">
-        <v>153</v>
       </c>
       <c r="AH49" s="87" t="s">
         <v>1</v>
@@ -11450,77 +11429,79 @@
         <v>1</v>
       </c>
       <c r="C50" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="D50" s="40" t="s">
+      <c r="F50" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="L50" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="M50" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="O50" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="P50" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="R50" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="F50" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="I50" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="L50" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="M50" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="O50" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="P50" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="R50" s="40" t="s">
+      <c r="S50" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="S50" s="40" t="s">
+      <c r="U50" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="V50" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="U50" s="40"/>
-      <c r="V50" s="40" t="s">
+      <c r="X50" s="81" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE50" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF50" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG50" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH50" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI50" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="X50" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y50" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE50" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF50" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG50" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH50" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI50" s="44" t="s">
+      <c r="AK50" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL50" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="AK50" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL50" s="40" t="s">
+      <c r="AM50" s="40" t="s">
         <v>160</v>
-      </c>
-      <c r="AM50" s="40" t="s">
-        <v>161</v>
       </c>
       <c r="AX50" s="3" t="s">
         <v>1</v>
@@ -11569,7 +11550,9 @@
       <c r="S51" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="U51" s="41"/>
+      <c r="U51" s="41" t="s">
+        <v>1</v>
+      </c>
       <c r="V51" s="41" t="s">
         <v>1</v>
       </c>
@@ -11604,17 +11587,13 @@
         <v>1</v>
       </c>
       <c r="AP51" s="43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AQ51" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AT51" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="AU51" s="44" t="s">
-        <v>1</v>
-      </c>
+      <c r="AT51" s="43"/>
+      <c r="AU51" s="44"/>
       <c r="AX51" s="3" t="s">
         <v>1</v>
       </c>
@@ -11662,7 +11641,9 @@
       <c r="S52" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="U52" s="42"/>
+      <c r="U52" s="42" t="s">
+        <v>1</v>
+      </c>
       <c r="V52" s="42" t="s">
         <v>1</v>
       </c>
@@ -11702,12 +11683,8 @@
       <c r="AQ52" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="AT52" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="AU52" s="46" t="s">
-        <v>1</v>
-      </c>
+      <c r="AT52" s="45"/>
+      <c r="AU52" s="46"/>
       <c r="AX52" s="3" t="s">
         <v>1</v>
       </c>
@@ -11717,88 +11694,82 @@
         <v>1</v>
       </c>
       <c r="C53" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="D53" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="F53" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="I53" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="D53" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="F53" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" s="40" t="s">
+      <c r="J53" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="L53" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="M53" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="O53" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="P53" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="R53" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="I53" s="40" t="s">
+      <c r="S53" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="J53" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="L53" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="M53" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="O53" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="P53" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q53" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="R53" s="40" t="s">
+      <c r="U53" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="V53" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="S53" s="40" t="s">
+      <c r="X53" s="81" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y53" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE53" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF53" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG53" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH53" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI53" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="U53" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="V53" s="40" t="s">
+      <c r="AL53" s="40"/>
+      <c r="AM53" s="40"/>
+      <c r="AP53" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="X53" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y53" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE53" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF53" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG53" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH53" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI53" s="44" t="s">
+      <c r="AQ53" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="AL53" s="40" t="s">
+      <c r="AT53" s="40"/>
+      <c r="AU53" s="40" t="s">
         <v>171</v>
-      </c>
-      <c r="AM53" s="40" t="s">
-        <v>171</v>
-      </c>
-      <c r="AP53" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="AQ53" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="AT53" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="AU53" s="40" t="s">
-        <v>175</v>
       </c>
       <c r="AX53" s="3" t="s">
         <v>1</v>
@@ -11874,21 +11845,15 @@
       <c r="AI54" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="AL54" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM54" s="41" t="s">
-        <v>1</v>
-      </c>
+      <c r="AL54" s="41"/>
+      <c r="AM54" s="41"/>
       <c r="AP54" s="41" t="s">
         <v>1</v>
       </c>
       <c r="AQ54" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="AT54" s="41" t="s">
-        <v>1</v>
-      </c>
+      <c r="AT54" s="41"/>
       <c r="AU54" s="41" t="s">
         <v>1</v>
       </c>
@@ -11966,21 +11931,15 @@
       <c r="AI55" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="AL55" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM55" s="42" t="s">
-        <v>1</v>
-      </c>
+      <c r="AL55" s="42"/>
+      <c r="AM55" s="42"/>
       <c r="AP55" s="42" t="s">
         <v>1</v>
       </c>
       <c r="AQ55" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="AT55" s="42" t="s">
-        <v>1</v>
-      </c>
+      <c r="AT55" s="42"/>
       <c r="AU55" s="42" t="s">
         <v>1</v>
       </c>
@@ -11993,91 +11952,91 @@
         <v>1</v>
       </c>
       <c r="C56" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="F56" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="G56" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="I56" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="J56" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="L56" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="M56" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="O56" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="P56" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="R56" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="D56" s="40" t="s">
+      <c r="S56" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="F56" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="G56" s="40" t="s">
+      <c r="T56" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="U56" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="V56" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="I56" s="40" t="s">
+      <c r="X56" s="81" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE56" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF56" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG56" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH56" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI56" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="J56" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="L56" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="M56" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="O56" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="P56" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="R56" s="40" t="s">
+      <c r="AL56" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="S56" s="40" t="s">
+      <c r="AM56" s="40" t="s">
         <v>181</v>
       </c>
-      <c r="T56" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="U56" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="V56" s="40" t="s">
+      <c r="AP56" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="X56" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y56" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE56" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF56" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG56" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH56" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI56" s="44" t="s">
+      <c r="AQ56" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="AL56" s="40" t="s">
+      <c r="AS56" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT56" s="40" t="s">
         <v>184</v>
       </c>
-      <c r="AM56" s="40" t="s">
+      <c r="AU56" s="40" t="s">
         <v>185</v>
-      </c>
-      <c r="AP56" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="AQ56" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="AS56" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="AT56" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="AU56" s="40" t="s">
-        <v>189</v>
       </c>
       <c r="AX56" s="3" t="s">
         <v>1</v>
@@ -12278,13 +12237,13 @@
         <v>1</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D59" s="47" t="s">
         <v>1</v>
       </c>
       <c r="G59" s="49" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H59" s="49" t="s">
         <v>1</v>
@@ -12293,13 +12252,13 @@
         <v>1</v>
       </c>
       <c r="U59" s="47" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="V59" s="47" t="s">
         <v>1</v>
       </c>
       <c r="AK59" s="49" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AL59" s="49" t="s">
         <v>1</v>
@@ -12308,7 +12267,7 @@
         <v>1</v>
       </c>
       <c r="AT59" s="47" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="AU59" s="47" t="s">
         <v>1</v>
@@ -12330,37 +12289,37 @@
         <v>1</v>
       </c>
       <c r="C61" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="D61" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="O61" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="P61" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="R61" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="S61" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM61" s="49" t="s">
         <v>194</v>
       </c>
-      <c r="D61" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" s="8" t="s">
+      <c r="AN61" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO61" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT61" s="49" t="s">
         <v>195</v>
-      </c>
-      <c r="O61" s="48" t="s">
-        <v>196</v>
-      </c>
-      <c r="P61" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="R61" s="48" t="s">
-        <v>197</v>
-      </c>
-      <c r="S61" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM61" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="AN61" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO61" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="AT61" s="49" t="s">
-        <v>199</v>
       </c>
       <c r="AU61" s="49" t="s">
         <v>1</v>
@@ -12376,104 +12335,102 @@
       <c r="B62" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C62" s="40" t="s">
+      <c r="C62" s="40"/>
+      <c r="D62" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="F62" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="G62" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="L62" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="M62" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="O62" s="40" t="s">
+        <v>198</v>
+      </c>
+      <c r="P62" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="R62" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="S62" s="40" t="s">
         <v>200</v>
       </c>
-      <c r="D62" s="40" t="s">
+      <c r="T62" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="U62" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="V62" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="X62" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="F62" s="40" t="s">
+      <c r="Y62" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z62" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="G62" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="L62" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="M62" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="O62" s="40" t="s">
+      <c r="AA62" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB62" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC62" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD62" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE62" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF62" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG62" s="31" t="s">
         <v>203</v>
       </c>
-      <c r="P62" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q62" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="R62" s="40" t="s">
+      <c r="AH62" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI62" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="S62" s="40" t="s">
+      <c r="AK62" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL62" s="40" t="s">
         <v>205</v>
       </c>
-      <c r="T62" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="U62" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="V62" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="X62" s="31" t="s">
+      <c r="AM62" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="Y62" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z62" s="31" t="s">
+      <c r="AP62" s="40" t="s">
         <v>207</v>
       </c>
-      <c r="AA62" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB62" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC62" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD62" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE62" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF62" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG62" s="31" t="s">
+      <c r="AQ62" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="AH62" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI62" s="44" t="s">
+      <c r="AT62" s="40" t="s">
         <v>209</v>
       </c>
-      <c r="AK62" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL62" s="40" t="s">
+      <c r="AU62" s="40" t="s">
         <v>210</v>
-      </c>
-      <c r="AM62" s="40" t="s">
-        <v>211</v>
-      </c>
-      <c r="AP62" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="AQ62" s="40" t="s">
-        <v>213</v>
-      </c>
-      <c r="AT62" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="AU62" s="40" t="s">
-        <v>215</v>
       </c>
       <c r="AX62" s="3" t="s">
         <v>1</v>
@@ -12483,9 +12440,7 @@
       <c r="B63" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C63" s="41" t="s">
-        <v>1</v>
-      </c>
+      <c r="C63" s="41"/>
       <c r="D63" s="41" t="s">
         <v>1</v>
       </c>
@@ -12590,9 +12545,7 @@
       <c r="B64" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C64" s="42" t="s">
-        <v>1</v>
-      </c>
+      <c r="C64" s="42"/>
       <c r="D64" s="42" t="s">
         <v>1</v>
       </c>
@@ -12698,97 +12651,97 @@
         <v>1</v>
       </c>
       <c r="C65" s="40" t="s">
+        <v>211</v>
+      </c>
+      <c r="D65" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F65" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="G65" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="J65" s="93" t="s">
+        <v>214</v>
+      </c>
+      <c r="L65" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="M65" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="O65" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="P65" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="D65" s="40" t="s">
+      <c r="R65" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="F65" s="40" t="s">
+      <c r="S65" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="G65" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="J65" s="93" t="s">
+      <c r="U65" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="V65" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="X65" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y65" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z65" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA65" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB65" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC65" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD65" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE65" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF65" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG65" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH65" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK65" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL65" s="40" t="s">
         <v>219</v>
       </c>
-      <c r="L65" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="M65" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="O65" s="40" t="s">
+      <c r="AM65" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="P65" s="40" t="s">
+      <c r="AP65" s="40" t="s">
         <v>221</v>
       </c>
-      <c r="R65" s="40" t="s">
+      <c r="AQ65" s="40" t="s">
         <v>222</v>
       </c>
-      <c r="S65" s="40" t="s">
+      <c r="AT65" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU65" s="40" t="s">
         <v>223</v>
-      </c>
-      <c r="U65" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="V65" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="X65" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y65" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z65" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA65" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB65" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC65" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD65" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE65" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF65" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG65" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH65" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK65" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL65" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="AM65" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="AP65" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="AQ65" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="AT65" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AU65" s="40" t="s">
-        <v>228</v>
       </c>
       <c r="AX65" s="3" t="s">
         <v>1</v>
@@ -13001,85 +12954,85 @@
         <v>1</v>
       </c>
       <c r="C68" s="43" t="s">
+        <v>224</v>
+      </c>
+      <c r="D68" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="G68" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="J68" s="87" t="s">
+        <v>1</v>
+      </c>
+      <c r="L68" s="95" t="s">
+        <v>1</v>
+      </c>
+      <c r="M68" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="O68" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="P68" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="R68" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="S68" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="U68" s="95" t="s">
+        <v>1</v>
+      </c>
+      <c r="V68" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="X68" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y68" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z68" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA68" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB68" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC68" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD68" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE68" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF68" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG68" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH68" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP68" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="AQ68" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT68" s="43" t="s">
         <v>229</v>
-      </c>
-      <c r="D68" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="43" t="s">
-        <v>230</v>
-      </c>
-      <c r="G68" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="J68" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="L68" s="95" t="s">
-        <v>1</v>
-      </c>
-      <c r="M68" s="96" t="s">
-        <v>1</v>
-      </c>
-      <c r="O68" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="P68" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="R68" s="43" t="s">
-        <v>232</v>
-      </c>
-      <c r="S68" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="U68" s="95" t="s">
-        <v>1</v>
-      </c>
-      <c r="V68" s="96" t="s">
-        <v>1</v>
-      </c>
-      <c r="X68" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y68" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z68" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA68" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB68" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC68" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD68" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE68" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF68" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG68" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH68" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="AP68" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="AQ68" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="AT68" s="43" t="s">
-        <v>234</v>
       </c>
       <c r="AU68" s="44" t="s">
         <v>1</v>
@@ -13655,7 +13608,7 @@
   <phoneticPr fontId="96" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CV49 A53:CV75 A50:T52 W50:CV52" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CV14 A56:CV61 A53:AK55 AU53:CV55 A18:CV50 A15:BJ17 BL15:CV17 A51:AS52 AV51:CV52 A65:CV75 A62:B64 D62:CV64 AN53:AS55" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dk18.xlsx
+++ b/dk18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676029D7-8990-45CC-92D1-12DF42DC3DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC86619F-9685-44BD-BC4C-9F7F8FB2063B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-48" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3228" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3229" uniqueCount="231">
   <si>
     <t>가산DK 18층 라운지</t>
   </si>
@@ -726,6 +726,10 @@
   </si>
   <si>
     <t>박성범</t>
+  </si>
+  <si>
+    <t>신현이</t>
+    <phoneticPr fontId="95" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2855,7 +2859,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3146,6 +3150,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="92" fillId="71" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3943,8 +3950,12 @@
       <c r="BI4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="BK4" s="42"/>
-      <c r="BL4" s="43"/>
+      <c r="BK4" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="BL4" s="43" t="s">
+        <v>1</v>
+      </c>
       <c r="BO4" s="42" t="s">
         <v>11</v>
       </c>
@@ -4082,8 +4093,12 @@
       <c r="BD5" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="BK5" s="44"/>
-      <c r="BL5" s="45"/>
+      <c r="BK5" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL5" s="45" t="s">
+        <v>1</v>
+      </c>
       <c r="BO5" s="44" t="s">
         <v>1</v>
       </c>
@@ -4248,9 +4263,7 @@
       <c r="BK6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="BL6" s="39" t="s">
-        <v>30</v>
-      </c>
+      <c r="BL6" s="39"/>
       <c r="BO6" s="39" t="s">
         <v>31</v>
       </c>
@@ -4418,9 +4431,7 @@
       <c r="BK7" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="BL7" s="40" t="s">
-        <v>1</v>
-      </c>
+      <c r="BL7" s="40"/>
       <c r="BO7" s="40" t="s">
         <v>1</v>
       </c>
@@ -4588,9 +4599,7 @@
       <c r="BK8" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="BL8" s="41" t="s">
-        <v>1</v>
-      </c>
+      <c r="BL8" s="41"/>
       <c r="BO8" s="41" t="s">
         <v>1</v>
       </c>
@@ -5640,8 +5649,8 @@
       <c r="BH15" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="BK15" s="39" t="s">
-        <v>1</v>
+      <c r="BK15" s="98" t="s">
+        <v>230</v>
       </c>
       <c r="BL15" s="39" t="s">
         <v>78</v>
@@ -13643,7 +13652,7 @@
   <phoneticPr fontId="95" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CV3 A6:CV75 A4:BJ5 BM4:CV5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CV3 A16:CV75 A15:BJ15 BL15:CV15 A5:CV5 A4:BJ4 BL4:CV4 A9:CV14 A6:BK8 BM6:CV8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>